--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K7" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="K8" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="K9" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2087,7 +2087,7 @@
       </c>
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="K11" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K12" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2087,7 +2087,7 @@
       </c>
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="K11" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K12" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2240,7 +2240,7 @@
       </c>
       <c r="K13" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2291,7 +2291,7 @@
       </c>
       <c r="K14" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K15" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="K16" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="✅ Existing Blogs Audit" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📅 180-Day Calendar (Deduped)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="📊 Summary &amp; Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✅ Existing Blogs Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 180-Day Calendar (Deduped)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Summary &amp; Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K17" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="K18" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>

--- a/Maxinor_180Day_Deduped_v2.xlsx
+++ b/Maxinor_180Day_Deduped_v2.xlsx
@@ -2546,7 +2546,7 @@
       </c>
       <c r="K19" s="28" t="inlineStr">
         <is>
-          <t>⬜ Pending</t>
+          <t>✅ Done</t>
         </is>
       </c>
     </row>
